--- a/www/download/IND.gdp.s.us.zdW16.xlsx
+++ b/www/download/IND.gdp.s.us.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>375111.187748</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356928.13926</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>397179.72672</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>512423.848344</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>623438.992442</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>701308.09172</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>754671.3759</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>912441.578344</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>1005074.072665</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>954678.206448</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1209750.812837</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1.442</t>
+          <t>1441861.11828</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1477848.366</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>1432605.682224</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1357150.478885</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175648.30844</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176084.09512</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>190900.092</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>233417.12464</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267700.9629</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>279646.06098</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>298435.52816</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>345265.6794</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>383192.37764</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>355343.71136</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>347747.0184</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382594.8192</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>362178.95296</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>381886.65516</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>389663.9292</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>212879.6404</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>213688.99572</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>233176.07136</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>287112.92624</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>332176.28038</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>346475.38068</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>366416.47448</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>422059.04295</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>466256.54304</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436009.45872</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>432885.72609</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>472784.8656</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>445371.16624</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>466560.06909</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>476145.5594</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11591.54944</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12497.2124389638</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14675.7091681221</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18471.0162814454</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22390.6500943455</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25414.35039</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28973.6672060623</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38092.713971269</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46273.6134409262</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45084.53884</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43370.7490745452</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49797.0673272613</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46230.762423257</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47925.0499127555</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49340.6960220562</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>573780.768611696</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>488838.113303252</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>461769.989325666</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>493897.597673764</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>590198.131782251</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>778200.446798215</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>948549.86007381</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>1204191.40965481</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1440132.25699798</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1438821.62547184</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>1877773.048032</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2.223</t>
+          <t>2222907.22218</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.092</t>
+          <t>2092195.693</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>2105490.766269</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.072</t>
+          <t>2071925.52268817</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>698250.313844531</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>693677.223165077</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>709446.68883668</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>840602.261666402</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>957996.441598153</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.094</t>
+          <t>1093591.28017652</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.236</t>
+          <t>1236070.94033146</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1372536.99614844</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1459758.27088984</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1294742.235942</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.519</t>
+          <t>1518658.742901</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1.677</t>
+          <t>1676666.88843</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.718</t>
+          <t>1717801.83628552</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1730180.25531501</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.676</t>
+          <t>1675520.77553332</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.198</t>
+          <t>1198452.28731382</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1324831.83964957</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1453811.41873581</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1640969.79297211</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.932</t>
+          <t>1931618.10305032</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2.257</t>
+          <t>2257160.588159</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>2713187.017772</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>3495059.9684464</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4.521</t>
+          <t>4521311.99515283</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4990237.6414066</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5.931</t>
+          <t>5931147.01080161</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>7.363</t>
+          <t>7362930.74985253</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>8.319</t>
+          <t>8318792.56141102</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9380358.56434463</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>10.284</t>
+          <t>10283983.0468709</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9211.89404</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9539.77606102738</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10416.988556634</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13172.93712</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15663.5302513263</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16852.3004120929</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18294.6261617683</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21436.1984238383</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24725.5786317324</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23440.2056634204</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23090.7792783981</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24986.3638177726</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22913.6329215849</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22078.9301937709</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21050.9211352384</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56407.6395916</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61663.864134</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75236.2149858</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91165.331412</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108125.136804</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123247.7356495</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141471.5085944</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171753.4164472</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215178.9375774</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>187596.4667668</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188037.9222925</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>205910.1128805</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186015.2702852</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>186867.5757735</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186073.360414</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1763371.2932</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.764</t>
+          <t>1764269.308</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1889634.0864</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.268</t>
+          <t>2268128.3968</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.559</t>
+          <t>2559480.9814</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2590323.1926</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>2718338.8432</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>3.099</t>
+          <t>3099193.88</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3389701.282</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3.079</t>
+          <t>3078652.7728</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>3.078</t>
+          <t>3077871.0615</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3379884.576</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3180034.176</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>3.369</t>
+          <t>3369203.766</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>3.485</t>
+          <t>3484775.065</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141845.064234</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>142032.862601</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153959.087642</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>187948.125558</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>215627.963152</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225202.480917</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>240539.808075</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271418.07173</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303858.68595</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>276252.93942</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>276192.439045</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>294901.550396727</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>280468.126697</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>292679.055975</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299877.694863019</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>541526.0756</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>570339.5744</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>645258.528</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>823157.272</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>965506.4727</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.038</t>
+          <t>1037886.6927</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1130155.5152</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1333297.7775</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1508558.3776</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>1403338.9656</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.312</t>
+          <t>1312327.6641</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1369339.632</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1229733.472</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1250131.2333</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1259828.5065</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5067.32435504318</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5538.74449774145</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6507.12168046594</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8790.81666603235</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10674.6119992857</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12379.4174939008</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14877.84174339</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19507.1802937199</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21560.3440027539</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17149.7598310545</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17070.8384016147</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20346.8248140884</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19900.4469653434</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22104.9213570017</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23393.7450895794</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110093.12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113840.6116</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122947.8576</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149593.2816</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172593.6128</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>178678.8861</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>188936.41</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>224287.807</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250603.7288</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>220863.7904</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216911.034</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237271.968</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221521.3616</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>231629.9367</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234731.3365</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.231</t>
+          <t>1231216.0632</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1245281.6464</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1358494.3488</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1669662.512</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>1914899.4648</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.981</t>
+          <t>1980806.256</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.084</t>
+          <t>2083771.1592</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2.394</t>
+          <t>2394018.1805</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.642</t>
+          <t>2641961.27</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.445</t>
+          <t>2444693.856</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.388</t>
+          <t>2387568.4659</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2.574</t>
+          <t>2574498.432</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.407</t>
+          <t>2407007.2752</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2.522</t>
+          <t>2522488.2201</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2.538</t>
+          <t>2537743.21407052</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1387317.97161</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1372015.4874</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1505418.4902</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.742</t>
+          <t>1741769.35581</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.057</t>
+          <t>2057122.3908</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.171</t>
+          <t>2171349.4548</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>2325106.08183</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2.664</t>
+          <t>2664476.2816</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.538</t>
+          <t>2538021.4462</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2109712.23136</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2.161</t>
+          <t>2161065.97584</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2.314</t>
+          <t>2314445.4116</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.355</t>
+          <t>2355415.55056</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2420100.54558</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.666</t>
+          <t>2666095.56732</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117967.472659433</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121327.484534647</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137866.000495132</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181572.818277982</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217400.613164357</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>222470.794313911</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>242390.400028724</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>281317.923918386</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>314484.090831784</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>296242.805864476</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264667.033661896</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>253218.067739234</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217104.645182509</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>212473.312417871</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>208343.667265509</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40405.09275</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46406.31903144</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58833.47551104</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73064.74541997</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88775.98056145</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97088.462976</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>99687.42213732</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119649.21779376</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>135824.14114731</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111063.51056927</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110432.546455</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119540.77507255</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106878.60539626</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113315.00671478</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116649.42960672</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177730.192743138</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172064.619511674</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>210125.57295406</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>250151.943131748</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273969.234653379</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303947.666221749</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>385676.363477963</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>455189.576572602</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538492.47596642</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564408.497206022</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>735405.288394</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>875658.9162447</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>898513.2400055</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>895520.14240908</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>868868.8196628</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>457035.091692524</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>473243.243242603</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>493672.137855166</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>576247.711586149</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>671188.524530264</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>786134.282420629</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>891667.802372195</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>1135324.37948551</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1253253.31063191</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>1290543.6293736</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1618577.39840716</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1.844</t>
+          <t>1843958.28340608</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.823</t>
+          <t>1823184.12204255</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>1886273.55519253</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1.994</t>
+          <t>1994314.19233914</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89127.95416</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97169.55496</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113921.25456</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>146268.00608</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170850.16256</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185194.73544</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>203839.00084</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239540.9238</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246206.0368</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>211851.9876</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200747.83446</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223065.7728</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>205731.42656</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>217768.29138</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>227662.388</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.026</t>
+          <t>1025834.02288</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1049855.09896</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>1148752.04208</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.424</t>
+          <t>1423557.39568</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1627502.5893</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.672</t>
+          <t>1672451.34342</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>1742633.80508</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>1.982</t>
+          <t>1982454.2895</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.168</t>
+          <t>2167705.63408</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.984</t>
+          <t>1984002.29544</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>1914876.34362</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2.049</t>
+          <t>2048646.072</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1862225.7368</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1.921</t>
+          <t>1920990.00357</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1925309.48981919</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.638</t>
+          <t>4637896.423278</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4.046</t>
+          <t>4046327.518474</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3.886</t>
+          <t>3886030.554791</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4199718.158394</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4.554</t>
+          <t>4553931.41858948</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4530129.95094718</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4310210.37749763</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4.311</t>
+          <t>4310742.49993999</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4.796</t>
+          <t>4796485.14136</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4.929</t>
+          <t>4929250.54416</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>5.411</t>
+          <t>5411384.96780317</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>5.838</t>
+          <t>5838375.60511275</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>5.872</t>
+          <t>5871593.42879351</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4820354.38468313</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>4.438</t>
+          <t>4437887.09869627</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>504456.9399408</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>477019.626084</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>543811.8137298</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>608985.753516</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>690742.7473884</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810642.8932745</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>912844.433718</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>1013652.06512</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>921408.396564</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>822434.6256322</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>991191.851424</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>1092493.561812</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.112</t>
+          <t>1111508.8081669</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1191047.7277062</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>1287093.3852255</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10253.4912648133</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10906.8243319947</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12764.04165454</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16896.7398876302</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20523.1061</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23649.8110463389</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27289.0738021863</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35737.7431480007</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43165.8952481186</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33893.8462942206</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33420.0419970678</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39181.5984</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38738.0931954663</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42038.7056007151</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43718.6263603348</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18941.9002274947</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18993.3780823003</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21108.43968</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26322.26940379</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30728.2714529963</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32991.4987327918</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37786.2720125805</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45274.7416</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49843.49996</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45472.1537941048</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47305.2627662803</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52919.8461009505</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50225.8315735393</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55429.7093644472</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58245.3736021142</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7111.79530539807</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7537.10092</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8650.06512</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10615.5200321462</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13019.3597195319</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15157.9340629513</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19142.3467107872</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27593.9965753122</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32262.9416857261</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23585.547898414</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21072.66435</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25061.107919238</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25162.0064153342</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26922.6808753305</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27753.6149885203</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>614135.895427753</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>656304.713577284</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>690230.575772909</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>677395.067442502</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>735640.484092552</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>828814.061341095</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>928915.04260097</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>1003194.04588196</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1082470.9259848</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>857448.20569631</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1007231.02010645</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1132750.68759739</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>1148698.33492421</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1209722.3909078</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.228</t>
+          <t>1227752.05128193</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3642.10776948187</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3626.31860214479</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3990.73595037522</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4839.96494025787</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5324.83078749739</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5580.06993289429</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5904.94862199242</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6910.04725622738</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7958.901847226</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7449.72516741671</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7641.00636035809</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8364.58547363882</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8152.80826089692</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8962.40789846854</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9457.72887404843</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>371279.8112</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>380275.3424</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>417565.6128</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>512320.48</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>581571.7621</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>605133.9723</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>647872.0216</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>750373.419</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>839660.5996</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>772285.4172</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>752675.4549</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>806789.28</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>750107.3536</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>779241.4254</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>792656.1675</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152788.830003739</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169973.552995028</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175686.337390116</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>191697.61617</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225238.629391</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267587.2808</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>300956.405332</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>375514.676898</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>469008.203776</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>390626.25574</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>420981.438816</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>463205.32618</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>440183.226496</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>467377.959295</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>484755.614040083</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103967.98952</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106706.156683258</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118004.43486124</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>144589.408899651</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165774.553</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171187.722878174</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180278.000396551</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208567.6238</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229469.525779466</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216899.232893162</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209892.293034214</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>214706.601718619</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>189329.288567618</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>198908.068976089</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>201499.850158618</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33855.9282132827</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36679.8974431496</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41590.3577190576</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53311.9534261215</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68261.9893938463</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88222.4438583678</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109194.49297093</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151949.534575816</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>186565.581347009</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151302.380153395</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150134.375601043</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162817.392341286</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150482.882772782</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168725.875063541</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176349.652656092</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232602.535880084</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273720.967630108</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311722.145334387</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>378794.54768016</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>515767.12938049</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>654819.83918064</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>845495.01103515</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1114178.64806395</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1428383.2626475</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1081377.71059968</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.296</t>
+          <t>1296436.81300515</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1603619.35328828</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>1723301.96855752</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.789</t>
+          <t>1788865.28847798</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1623896.15686002</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18433.8896655736</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19364.9017937135</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22506.3408147581</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30522.5401372103</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38646.5438564023</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43443.34995</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51529.5386207924</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69461.6249724713</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88043.4598372719</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81035.9224472636</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81406.59705</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88900.7383997552</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85216.1004090459</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89493.2372395871</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91105.6073</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17689.4540199267</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18269.0057236374</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20697.2725280493</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26051.527193368</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30276.0856134792</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31960.2474131956</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34829.4330608991</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42223.2564391536</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48874.2076521073</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44129.392863852</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41869.3532718963</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44690.5776</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40118.7454887903</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41133.78039</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42819.1138321417</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>230395.138155</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>212116.3600964</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>233323.19538</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>292578.170658</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>337583.65179</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>343431.253755</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>370709.317255</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>430725.616251</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>459105.828996</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>379515.592485</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>430262.047036</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>496789.030202</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>480556.789925</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>511805.763132</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>507219.250428</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>263237.344562156</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200936.879026552</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211186.631041659</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>271931.722454549</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>345511.718027433</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>425591.111894991</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>469354.616212552</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>581364.938355215</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>663767.445470711</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>558928.097829074</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>652970.771416704</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>690217.811900883</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>703301.895047276</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>731250.830686698</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>710919.200524792</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>321951.052355149</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>292064.3603755</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>299197.48373102</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>311335.464001395</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>340473.789719347</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>366612.11800914</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377798.069533676</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>391993.575299921</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>401654.218358346</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377714.272746528</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>432114.278490614</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>471263.066793375</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>476338.049571149</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>494432.012092711</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>510922.945205479</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>10.285</t>
+          <t>10284778</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10.622</t>
+          <t>10621824</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>10.978</t>
+          <t>10977513</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>11.511</t>
+          <t>11510670</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>12.275</t>
+          <t>12274925</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>13.094</t>
+          <t>13093722</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>13.856</t>
+          <t>13855889</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>14.478</t>
+          <t>14477638</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>14.719</t>
+          <t>14718578</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>14.419</t>
+          <t>14418744</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>14.964</t>
+          <t>14964371</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>15.518</t>
+          <t>15517927</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>16.155</t>
+          <t>16155253</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>16.663</t>
+          <t>16663162</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>17.348</t>
+          <t>17348070</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2.988</t>
+          <t>2988186.09702126</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2.976</t>
+          <t>2975564.63983902</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2.902</t>
+          <t>2901766.62555792</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>3.243</t>
+          <t>3242773.07776634</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>3.834</t>
+          <t>3833605.96402527</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>4.547</t>
+          <t>4546855.35921803</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5.321</t>
+          <t>5321482.32542044</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6319813.09397517</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>7.537</t>
+          <t>7537349.90733164</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>7.035</t>
+          <t>7034512.27976041</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>8.242</t>
+          <t>8241860.11794752</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>9.494</t>
+          <t>9494132.67138763</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10189621.2126757</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>10.529</t>
+          <t>10528582.5882739</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>10.689</t>
+          <t>10688523.5929504</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>31.645</t>
+          <t>31644539.2110633</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>31.479</t>
+          <t>31479455.7128878</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>32.776</t>
+          <t>32775645.9863482</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>36.712</t>
+          <t>36712161.167748</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>41.251</t>
+          <t>41251114.9209817</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>44.678</t>
+          <t>44677772.5653578</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>48.345</t>
+          <t>48344897.0666069</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>54.427</t>
+          <t>54426589.7731068</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>59.892</t>
+          <t>59891534.2789202</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>56.885</t>
+          <t>56884939.6962316</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>62.055</t>
+          <t>62054623.0228873</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>68.812</t>
+          <t>68812306.2629739</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>70.263</t>
+          <t>70262786.5881451</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>72.106</t>
+          <t>72105635.0325916</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>73.807</t>
+          <t>73806917.7970671</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18134.51656</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19350.7809845828</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22471.7163823032</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29067.719840004</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35177.2394252981</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38437.9877416706</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42717.971767504</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51219.3689371525</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60442.3184266741</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54281.241996528</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51009.6328350742</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53462.4313135533</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47879.9006979348</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48683.2849875546</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48159.9882282878</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>259530.985971618</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>267011.605034143</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>290286.575793508</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338784.159991228</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>378528.455501533</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>392457.802412324</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>412535.137763118</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>459284.451695462</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>533391.248073703</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>522616.412855948</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>561184.001993006</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>673542.680123105</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>642992.495646632</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>662515.924919476</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>680533.250223279</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151398.756208</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153747.9688</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173539.126849</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>201814.088954</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234961.359904</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>275533.95624</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308471.77881</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356664.311842</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>421510.298928</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>346705.705935</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>382032.299191</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>445879.819668</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456957.940824</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>468347.447642</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>449132.121946</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>gdp.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
